--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="554">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -312,7 +312,7 @@
     <t>Practitioner.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>
@@ -1580,7 +1580,7 @@
     <t>Practitioner.photo</t>
   </si>
   <si>
-    <t xml:space="preserve">Attachment
+    <t xml:space="preserve">Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
 </t>
   </si>
   <si>
@@ -1685,6 +1685,10 @@
   </si>
   <si>
     <t>Practitioner.qualification.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}
+</t>
   </si>
   <si>
     <t>Period during which the qualification is valid</t>
@@ -10230,17 +10234,17 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>228</v>
+        <v>535</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10307,10 +10311,10 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10318,10 +10322,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10344,13 +10348,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10401,7 +10405,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10419,7 +10423,7 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
@@ -10430,10 +10434,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10459,16 +10463,16 @@
         <v>527</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10517,7 +10521,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10532,13 +10536,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1709,7 +1709,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2073,7 +2073,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="106.66015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-practitioner-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
